--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-10</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>📈 매수 관찰 구간입니다.</t>
-  </si>
-  <si>
-    <t>⛔ 관망하십시오.</t>
   </si>
   <si>
     <t>⚪ 중립 구간</t>
@@ -504,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>104.67</v>
+        <v>104.1</v>
       </c>
       <c r="E2">
-        <v>55</v>
+        <v>55.5</v>
       </c>
       <c r="F2">
-        <v>14.54</v>
+        <v>13.35</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>64.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -534,10 +531,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -551,40 +548,40 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>21.39</v>
+        <v>21.24</v>
       </c>
       <c r="E3">
-        <v>46.8</v>
+        <v>49</v>
       </c>
       <c r="F3">
-        <v>6.95</v>
+        <v>12.33</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>52.9</v>
+        <v>60.4</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>48.11568981226033</v>
+      </c>
+      <c r="O3" t="s">
         <v>22</v>
-      </c>
-      <c r="N3">
-        <v>52.28493729186943</v>
-      </c>
-      <c r="O3" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>날짜</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
+    <t>⛔ 관망하십시오.</t>
   </si>
   <si>
     <t>⚪ 중립 구간</t>
@@ -501,13 +504,13 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>104.1</v>
+        <v>103.93</v>
       </c>
       <c r="E2">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="F2">
-        <v>13.35</v>
+        <v>13.16</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -522,7 +525,7 @@
         <v>83</v>
       </c>
       <c r="K2">
-        <v>66.8</v>
+        <v>66.3</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,10 +534,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -548,13 +551,13 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>21.24</v>
+        <v>21.32</v>
       </c>
       <c r="E3">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="F3">
-        <v>12.33</v>
+        <v>12.74</v>
       </c>
       <c r="G3">
         <v>60</v>
@@ -569,19 +572,19 @@
         <v>66</v>
       </c>
       <c r="K3">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -504,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>103.93</v>
+        <v>87.42</v>
       </c>
       <c r="E2">
-        <v>55.4</v>
+        <v>49.4</v>
       </c>
       <c r="F2">
-        <v>13.16</v>
+        <v>-16.48</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I2">
+        <v>80</v>
+      </c>
+      <c r="J2">
         <v>86</v>
       </c>
-      <c r="J2">
-        <v>83</v>
-      </c>
       <c r="K2">
-        <v>66.3</v>
+        <v>58.2</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -534,10 +531,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -551,40 +548,40 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>21.32</v>
+        <v>18.34</v>
       </c>
       <c r="E3">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="F3">
-        <v>12.74</v>
+        <v>-14.26</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I3">
+        <v>63</v>
+      </c>
+      <c r="J3">
         <v>70</v>
       </c>
-      <c r="J3">
-        <v>66</v>
-      </c>
       <c r="K3">
-        <v>59.9</v>
+        <v>51.4</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>47.37006702605126</v>
+      </c>
+      <c r="O3" t="s">
         <v>22</v>
-      </c>
-      <c r="N3">
-        <v>46.17217538625081</v>
-      </c>
-      <c r="O3" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>87.42</v>
+        <v>76.92</v>
       </c>
       <c r="E2">
-        <v>49.4</v>
+        <v>22.2</v>
       </c>
       <c r="F2">
-        <v>-16.48</v>
+        <v>-1.03</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>58.2</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>18.34</v>
+        <v>14.85</v>
       </c>
       <c r="E3">
-        <v>49.2</v>
+        <v>18.3</v>
       </c>
       <c r="F3">
-        <v>-14.26</v>
+        <v>-5.95</v>
       </c>
       <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>56</v>
+      </c>
+      <c r="I3">
+        <v>46</v>
+      </c>
+      <c r="J3">
+        <v>60</v>
+      </c>
+      <c r="K3">
         <v>40</v>
-      </c>
-      <c r="H3">
-        <v>63</v>
-      </c>
-      <c r="I3">
-        <v>63</v>
-      </c>
-      <c r="J3">
-        <v>70</v>
-      </c>
-      <c r="K3">
-        <v>51.4</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>날짜</t>
   </si>
@@ -61,25 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>NuScale Power Corporation</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
   </si>
   <si>
-    <t>NuScale Power Corporation</t>
+    <t>SMR</t>
   </si>
   <si>
     <t>OKLO</t>
   </si>
   <si>
-    <t>SMR</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>⚪ 중립 구간</t>
@@ -501,28 +504,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>76.92</v>
+        <v>16.31</v>
       </c>
       <c r="E2">
-        <v>22.2</v>
+        <v>27.3</v>
       </c>
       <c r="F2">
-        <v>-1.03</v>
+        <v>1.43</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H2">
+        <v>53</v>
+      </c>
+      <c r="I2">
         <v>60</v>
       </c>
-      <c r="I2">
-        <v>66</v>
-      </c>
       <c r="J2">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,10 +534,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -548,40 +551,40 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>14.85</v>
+        <v>77.8</v>
       </c>
       <c r="E3">
-        <v>18.3</v>
+        <v>27.1</v>
       </c>
       <c r="F3">
-        <v>-5.95</v>
+        <v>-4.32</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>날짜</t>
   </si>
@@ -61,28 +61,25 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>Oklo Inc.</t>
   </si>
   <si>
     <t>NuScale Power Corporation</t>
   </si>
   <si>
-    <t>Oklo Inc.</t>
+    <t>OKLO</t>
   </si>
   <si>
     <t>SMR</t>
   </si>
   <si>
-    <t>OKLO</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
-  </si>
-  <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>⚪ 중립 구간</t>
@@ -504,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>16.31</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E2">
-        <v>27.3</v>
+        <v>62.7</v>
       </c>
       <c r="F2">
-        <v>1.43</v>
+        <v>29.03</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>45.5</v>
+        <v>58.9</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -534,10 +531,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -551,40 +548,40 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>77.8</v>
+        <v>19.57</v>
       </c>
       <c r="E3">
-        <v>27.1</v>
+        <v>60.5</v>
       </c>
       <c r="F3">
-        <v>-4.32</v>
+        <v>35.15</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>39.5</v>
+        <v>50.9</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>45.04298008974126</v>
+      </c>
+      <c r="O3" t="s">
         <v>22</v>
-      </c>
-      <c r="N3">
-        <v>41.50472307187444</v>
-      </c>
-      <c r="O3" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -522,7 +522,7 @@
         <v>76</v>
       </c>
       <c r="K2">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -569,7 +569,7 @@
         <v>56</v>
       </c>
       <c r="K3">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -501,16 +504,16 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>95.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E2">
-        <v>62.7</v>
+        <v>63.3</v>
       </c>
       <c r="F2">
-        <v>29.03</v>
+        <v>36.27</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>70</v>
@@ -519,10 +522,10 @@
         <v>76</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>59</v>
+        <v>61.5</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,10 +534,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -548,40 +551,40 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19.57</v>
+        <v>19.47</v>
       </c>
       <c r="E3">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="F3">
-        <v>35.15</v>
+        <v>36.06</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>51</v>
+        <v>55.1</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -504,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>97.59999999999999</v>
+        <v>105.31</v>
       </c>
       <c r="E2">
-        <v>63.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F2">
-        <v>36.27</v>
+        <v>35.36</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>61.5</v>
+        <v>56.3</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -534,10 +531,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -551,40 +548,40 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19.47</v>
+        <v>20.51</v>
       </c>
       <c r="E3">
-        <v>61.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F3">
-        <v>36.06</v>
+        <v>25.75</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
         <v>53</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>55.1</v>
+        <v>51.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>50.40292622392195</v>
+      </c>
+      <c r="O3" t="s">
         <v>22</v>
-      </c>
-      <c r="N3">
-        <v>43.60821037092016</v>
-      </c>
-      <c r="O3" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -522,7 +522,7 @@
         <v>73</v>
       </c>
       <c r="K2">
-        <v>56.3</v>
+        <v>56.4</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -569,7 +569,7 @@
         <v>53</v>
       </c>
       <c r="K3">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>105.31</v>
+        <v>102.5</v>
       </c>
       <c r="E2">
-        <v>76.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F2">
-        <v>35.36</v>
+        <v>14.73</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>56.4</v>
+        <v>58.8</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>20.51</v>
+        <v>19.72</v>
       </c>
       <c r="E3">
-        <v>74.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F3">
-        <v>25.75</v>
+        <v>5.01</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>51.4</v>
+        <v>54.8</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -501,13 +504,13 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>102.5</v>
+        <v>97.09</v>
       </c>
       <c r="E2">
-        <v>69.90000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="F2">
-        <v>14.73</v>
+        <v>1.56</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -516,13 +519,13 @@
         <v>66</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>58.8</v>
+        <v>60.1</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,10 +534,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -548,40 +551,40 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19.72</v>
+        <v>19.23</v>
       </c>
       <c r="E3">
-        <v>67.90000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="F3">
-        <v>5.01</v>
+        <v>-1.74</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I3">
         <v>56</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>54.8</v>
+        <v>50.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -504,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>97.09</v>
+        <v>94.95</v>
       </c>
       <c r="E2">
-        <v>62.7</v>
+        <v>66</v>
       </c>
       <c r="F2">
-        <v>1.56</v>
+        <v>-9.84</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>73</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>60.1</v>
+        <v>56.3</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -534,10 +531,10 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -551,40 +548,40 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19.23</v>
+        <v>20.19</v>
       </c>
       <c r="E3">
-        <v>63.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F3">
-        <v>-1.74</v>
+        <v>-1.56</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
       <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>40.49436870247035</v>
+      </c>
+      <c r="O3" t="s">
         <v>22</v>
-      </c>
-      <c r="N3">
-        <v>43.1153238131143</v>
-      </c>
-      <c r="O3" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>94.95</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="E2">
-        <v>66</v>
+        <v>34.6</v>
       </c>
       <c r="F2">
-        <v>-9.84</v>
+        <v>2.52</v>
       </c>
       <c r="G2">
+        <v>30</v>
+      </c>
+      <c r="H2">
+        <v>46</v>
+      </c>
+      <c r="I2">
         <v>50</v>
       </c>
-      <c r="H2">
-        <v>80</v>
-      </c>
-      <c r="I2">
-        <v>73</v>
-      </c>
       <c r="J2">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>56.3</v>
+        <v>35.1</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>20.19</v>
+        <v>13.05</v>
       </c>
       <c r="E3">
-        <v>73.59999999999999</v>
+        <v>22.8</v>
       </c>
       <c r="F3">
-        <v>-1.56</v>
+        <v>3.57</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>49.3</v>
+        <v>33.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>64.68000000000001</v>
+        <v>58.25</v>
       </c>
       <c r="E2">
-        <v>34.6</v>
+        <v>38.4</v>
       </c>
       <c r="F2">
-        <v>2.52</v>
+        <v>-7.47</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>35.1</v>
+        <v>30.7</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>13.05</v>
+        <v>11.67</v>
       </c>
       <c r="E3">
-        <v>22.8</v>
+        <v>27.6</v>
       </c>
       <c r="F3">
-        <v>3.57</v>
+        <v>-9.18</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K3">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -522,7 +522,7 @@
         <v>63</v>
       </c>
       <c r="K2">
-        <v>30.7</v>
+        <v>29.4</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -569,7 +569,7 @@
         <v>46</v>
       </c>
       <c r="K3">
-        <v>26.7</v>
+        <v>25.4</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>58.25</v>
+        <v>61.78</v>
       </c>
       <c r="E2">
-        <v>38.4</v>
+        <v>41.3</v>
       </c>
       <c r="F2">
-        <v>-7.47</v>
+        <v>-4.48</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K2">
-        <v>29.4</v>
+        <v>43.9</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>11.67</v>
+        <v>12.16</v>
       </c>
       <c r="E3">
-        <v>27.6</v>
+        <v>33.4</v>
       </c>
       <c r="F3">
-        <v>-9.18</v>
+        <v>-6.82</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I3">
+        <v>60</v>
+      </c>
+      <c r="J3">
         <v>56</v>
       </c>
-      <c r="J3">
-        <v>46</v>
-      </c>
       <c r="K3">
-        <v>25.4</v>
+        <v>36.7</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>61.78</v>
+        <v>61.38</v>
       </c>
       <c r="E2">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="F2">
-        <v>-4.48</v>
+        <v>-3.03</v>
       </c>
       <c r="G2">
         <v>30</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>43.9</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>12.16</v>
+        <v>12.03</v>
       </c>
       <c r="E3">
-        <v>33.4</v>
+        <v>33.1</v>
       </c>
       <c r="F3">
-        <v>-6.82</v>
+        <v>-3.99</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>36.7</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>61.38</v>
+        <v>62.76</v>
       </c>
       <c r="E2">
-        <v>41.1</v>
+        <v>43</v>
       </c>
       <c r="F2">
-        <v>-3.03</v>
+        <v>-4.4</v>
       </c>
       <c r="G2">
         <v>30</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J2">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>46</v>
+        <v>43.9</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>12.03</v>
+        <v>12.38</v>
       </c>
       <c r="E3">
-        <v>33.1</v>
+        <v>32.1</v>
       </c>
       <c r="F3">
-        <v>-3.99</v>
+        <v>-1.28</v>
       </c>
       <c r="G3">
         <v>20</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J3">
         <v>53</v>
       </c>
       <c r="K3">
-        <v>39</v>
+        <v>35.7</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>62.76</v>
+        <v>46.59</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>25.6</v>
       </c>
       <c r="F2">
-        <v>-4.4</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I2">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>43.9</v>
+        <v>42</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>12.38</v>
+        <v>9.16</v>
       </c>
       <c r="E3">
-        <v>32.1</v>
+        <v>20.4</v>
       </c>
       <c r="F3">
-        <v>-1.28</v>
+        <v>-10.63</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I3">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="K3">
-        <v>35.7</v>
+        <v>33.2</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>46.59</v>
+        <v>79.62</v>
       </c>
       <c r="E2">
-        <v>25.6</v>
+        <v>61.4</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>22.53</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J2">
         <v>50</v>
       </c>
       <c r="K2">
-        <v>42</v>
+        <v>55.7</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>9.16</v>
+        <v>13.52</v>
       </c>
       <c r="E3">
-        <v>20.4</v>
+        <v>59.2</v>
       </c>
       <c r="F3">
-        <v>-10.63</v>
+        <v>19.43</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I3">
         <v>33</v>
       </c>
       <c r="J3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3">
-        <v>33.2</v>
+        <v>48.9</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_SMR_분석.xlsx
+++ b/DECISION/미장_SMR_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-07</t>
   </si>
   <si>
     <t>Oklo Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>79.62</v>
+        <v>58.09</v>
       </c>
       <c r="E2">
-        <v>61.4</v>
+        <v>45.3</v>
       </c>
       <c r="F2">
-        <v>22.53</v>
+        <v>-13.14</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K2">
-        <v>55.7</v>
+        <v>32.3</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>13.52</v>
+        <v>10.5</v>
       </c>
       <c r="E3">
-        <v>59.2</v>
+        <v>45.9</v>
       </c>
       <c r="F3">
-        <v>19.43</v>
+        <v>-17.13</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I3">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>48.9</v>
+        <v>28.9</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>
